--- a/data/trans_camb/P1423-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1423-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,6</t>
+          <t>-0,56; 5,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,64</t>
+          <t>-0,71; 5,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 1,05</t>
+          <t>-3,17; 1,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 8,01</t>
+          <t>-3,51; 7,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 9,58</t>
+          <t>-1,69; 10,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -1,01</t>
+          <t>-9,69; -1,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 5,53</t>
+          <t>-0,76; 5,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 6,7</t>
+          <t>0,08; 6,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,59; -0,72</t>
+          <t>-5,58; -0,74</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 346,04</t>
+          <t>-22,89; 385,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,63; 396,76</t>
+          <t>-27,31; 383,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,21; 91,38</t>
+          <t>-83,85; 88,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,82; 103,31</t>
+          <t>-27,72; 98,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 131,23</t>
+          <t>-14,92; 133,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,91; -12,96</t>
+          <t>-71,38; -12,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 111,69</t>
+          <t>-10,71; 110,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 129,97</t>
+          <t>-0,38; 132,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-67,57; -12,95</t>
+          <t>-66,1; -14,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,05</t>
+          <t>-0,91; 4,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,2</t>
+          <t>-1,43; 2,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,94</t>
+          <t>0,67; 5,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 7,3</t>
+          <t>-0,61; 7,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,24</t>
+          <t>-2,66; 4,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 8,23</t>
+          <t>1,1; 8,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,76</t>
+          <t>0,04; 4,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,88</t>
+          <t>-1,28; 3,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,17</t>
+          <t>1,53; 6,01</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,04; 265,11</t>
+          <t>-31,94; 275,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,9; 253,11</t>
+          <t>-47,21; 158,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 393,99</t>
+          <t>14,56; 412,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 97,88</t>
+          <t>-7,6; 98,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 59,02</t>
+          <t>-26,77; 65,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 115,45</t>
+          <t>10,58; 116,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 96,84</t>
+          <t>0,09; 100,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 64,64</t>
+          <t>-18,57; 64,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,92; 129,04</t>
+          <t>21,36; 128,68</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,14</t>
+          <t>1,54; 7,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,86</t>
+          <t>-1,71; 1,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,35; 11,04</t>
+          <t>4,55; 11,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 9,66</t>
+          <t>0,73; 9,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 5,35</t>
+          <t>-2,58; 5,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 12,09</t>
+          <t>4,4; 12,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,15</t>
+          <t>1,9; 7,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,2</t>
+          <t>-1,52; 3,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 10,89</t>
+          <t>5,4; 10,83</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,43; 1864,95</t>
+          <t>14,35; 1918,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-96,23; 743,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>109,85; 3061,79</t>
+          <t>118,22; 2807,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 201,86</t>
+          <t>6,03; 190,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,05; 113,0</t>
+          <t>-30,14; 121,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,85; 254,13</t>
+          <t>47,13; 274,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,84; 250,13</t>
+          <t>36,62; 246,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 110,16</t>
+          <t>-29,93; 105,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>99,25; 370,12</t>
+          <t>104,73; 395,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,2</t>
+          <t>-2,04; 2,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,17</t>
+          <t>-1,4; 3,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,96</t>
+          <t>2,66; 9,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 13,23</t>
+          <t>5,44; 13,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,42</t>
+          <t>-1,0; 5,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 7,05</t>
+          <t>-0,63; 7,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,15</t>
+          <t>2,17; 7,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,78</t>
+          <t>-0,58; 3,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,45</t>
+          <t>2,07; 7,29</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-62,94; 345,19</t>
+          <t>-65,08; 290,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,67; 294,8</t>
+          <t>-50,32; 349,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42,38; 918,14</t>
+          <t>56,76; 893,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76,66; 429,86</t>
+          <t>77,55; 426,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 172,28</t>
+          <t>-17,07; 171,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 210,39</t>
+          <t>-10,67; 222,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,37; 297,58</t>
+          <t>48,53; 280,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 141,79</t>
+          <t>-15,98; 148,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40,6; 291,77</t>
+          <t>46,24; 300,06</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 5,49</t>
+          <t>-2,16; 5,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 6,16</t>
+          <t>-1,65; 6,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 0,73</t>
+          <t>-4,55; 0,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,28; 17,76</t>
+          <t>3,24; 16,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 8,56</t>
+          <t>-3,82; 8,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 0,54</t>
+          <t>-9,93; 0,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 9,86</t>
+          <t>1,83; 10,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 6,0</t>
+          <t>-1,25; 5,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,27</t>
+          <t>-5,96; 0,17</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-44,45; 292,51</t>
+          <t>-49,84; 331,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 347,76</t>
+          <t>-35,75; 361,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-85,5; 79,38</t>
+          <t>-87,52; 53,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,57; 235,99</t>
+          <t>23,17; 225,66</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 122,39</t>
+          <t>-28,58; 127,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-71,28; 5,18</t>
+          <t>-72,45; 6,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,29; 206,65</t>
+          <t>21,24; 204,62</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 112,38</t>
+          <t>-15,76; 120,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-66,31; 3,49</t>
+          <t>-64,5; 5,33</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,91; 8,22</t>
+          <t>1,85; 7,83</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,41</t>
+          <t>0,04; 4,16</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,28; 12,97</t>
+          <t>6,49; 12,91</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,64; 12,63</t>
+          <t>2,94; 12,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,44; 11,88</t>
+          <t>2,67; 11,73</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,96; 13,83</t>
+          <t>5,05; 13,51</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,93</t>
+          <t>3,12; 9,28</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,12</t>
+          <t>1,83; 7,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6,81; 12,26</t>
+          <t>6,56; 12,22</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>32,8; —</t>
+          <t>30,2; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-63,27; —</t>
+          <t>-79,24; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>288,77; —</t>
+          <t>216,38; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>29,59; 315,2</t>
+          <t>28,98; 327,98</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>23,23; 330,01</t>
+          <t>30,21; 327,45</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>54,75; 357,24</t>
+          <t>63,28; 381,21</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>66,74; 401,18</t>
+          <t>59,16; 430,36</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>41,37; 328,54</t>
+          <t>36,19; 336,58</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>147,16; 564,64</t>
+          <t>142,63; 586,33</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 4,39</t>
+          <t>0,15; 4,9</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,09</t>
+          <t>-2,3; 1,31</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,05</t>
+          <t>1,74; 7,01</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 3,89</t>
+          <t>-2,09; 4,04</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 3,52</t>
+          <t>-2,27; 3,9</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 8,27</t>
+          <t>-3,16; 8,46</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,47</t>
+          <t>-0,45; 3,47</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,72</t>
+          <t>-1,79; 2,04</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,1; 6,86</t>
+          <t>0,36; 6,8</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 211,59</t>
+          <t>-4,58; 245,98</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-63,53; 64,65</t>
+          <t>-62,41; 67,56</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>44,59; 334,5</t>
+          <t>42,03; 329,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 61,76</t>
+          <t>-22,38; 62,28</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 53,84</t>
+          <t>-24,97; 60,31</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 109,55</t>
+          <t>-32,48; 115,9</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 76,55</t>
+          <t>-7,12; 75,96</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 35,36</t>
+          <t>-28,7; 43,72</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,23; 141,04</t>
+          <t>10,62; 139,85</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,82; -0,58</t>
+          <t>-5,0; -0,69</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 0,83</t>
+          <t>-3,97; 0,49</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,28</t>
+          <t>-5,16; 0,58</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,7</t>
+          <t>-1,99; 3,91</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,09; 7,15</t>
+          <t>0,96; 7,09</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,85</t>
+          <t>1,47; 6,87</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,01</t>
+          <t>-2,51; 1,02</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,27</t>
+          <t>-0,69; 3,36</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 2,61</t>
+          <t>-2,67; 2,61</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-69,31; -13,72</t>
+          <t>-70,85; -13,4</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-53,81; 17,17</t>
+          <t>-55,78; 15,02</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-72,83; 5,22</t>
+          <t>-74,72; 10,4</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 63,26</t>
+          <t>-23,01; 60,95</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>12,23; 116,99</t>
+          <t>9,86; 115,26</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,0; 116,38</t>
+          <t>15,22; 115,72</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 17,62</t>
+          <t>-33,45; 17,65</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 56,82</t>
+          <t>-8,79; 58,72</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 42,39</t>
+          <t>-34,32; 42,04</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,07</t>
+          <t>0,09; 1,98</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,96</t>
+          <t>-0,68; 0,94</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,7</t>
+          <t>1,29; 3,7</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,09</t>
+          <t>2,34; 5,24</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,95</t>
+          <t>1,13; 4,07</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,04</t>
+          <t>1,16; 4,9</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,34</t>
+          <t>1,62; 3,31</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,17</t>
+          <t>0,68; 2,28</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,09</t>
+          <t>1,88; 4,14</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>5,29; 74,33</t>
+          <t>1,93; 73,93</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 36,47</t>
+          <t>-18,91; 34,96</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>39,35; 137,32</t>
+          <t>38,28; 132,47</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>27,61; 73,02</t>
+          <t>28,59; 76,61</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>13,9; 56,6</t>
+          <t>13,83; 60,88</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>17,09; 69,94</t>
+          <t>16,31; 69,48</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>27,76; 65,9</t>
+          <t>27,85; 64,98</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>9,31; 44,22</t>
+          <t>11,55; 45,31</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>33,4; 81,69</t>
+          <t>33,54; 82,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1423-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1423-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,9</t>
+          <t>-1,07</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,22</t>
+          <t>-5,23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,03</t>
+          <t>-3,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,29</t>
+          <t>-0,61; 5,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 5,9</t>
+          <t>-0,72; 5,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,2</t>
+          <t>-3,34; 1,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 7,57</t>
+          <t>-4,07; 7,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 10,18</t>
+          <t>-1,83; 9,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -1,27</t>
+          <t>-9,11; -1,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 5,49</t>
+          <t>-1,05; 5,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 6,58</t>
+          <t>0,19; 6,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; -0,74</t>
+          <t>-5,54; -0,77</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-33,96%</t>
+          <t>-40,22%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-50,76%</t>
+          <t>-50,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-47,52%</t>
+          <t>-48,15%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 385,12</t>
+          <t>-23,86; 402,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 383,52</t>
+          <t>-29,42; 379,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-83,85; 88,74</t>
+          <t>-84,4; 92,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,72; 98,68</t>
+          <t>-30,25; 92,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 133,43</t>
+          <t>-14,53; 132,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,38; -12,81</t>
+          <t>-69,74; -14,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 110,32</t>
+          <t>-16,4; 108,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 132,44</t>
+          <t>1,03; 130,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,1; -14,45</t>
+          <t>-66,83; -12,03</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>3,3</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,53</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>4,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,12</t>
+          <t>-0,91; 4,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,48</t>
+          <t>-1,29; 2,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,91</t>
+          <t>0,79; 6,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 7,14</t>
+          <t>-0,42; 7,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 4,66</t>
+          <t>-3,13; 4,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,06</t>
+          <t>1,06; 8,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,75</t>
+          <t>0,15; 5,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,03</t>
+          <t>-1,28; 3,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,01</t>
+          <t>1,91; 6,27</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126,85%</t>
+          <t>135,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>69,96%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,94; 275,31</t>
+          <t>-34,54; 253,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 158,7</t>
+          <t>-42,46; 185,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,56; 412,93</t>
+          <t>9,5; 362,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 98,15</t>
+          <t>-4,35; 99,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 65,58</t>
+          <t>-27,75; 58,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,58; 116,01</t>
+          <t>8,17; 112,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 100,31</t>
+          <t>1,41; 111,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 64,68</t>
+          <t>-19,2; 67,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,36; 128,68</t>
+          <t>26,57; 132,54</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,51</t>
+          <t>8,03</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,58</t>
+          <t>8,59</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8,14</t>
+          <t>8,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,39</t>
+          <t>1,53; 7,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,9</t>
+          <t>-1,88; 2,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 11,07</t>
+          <t>4,62; 11,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 9,76</t>
+          <t>0,53; 9,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 5,53</t>
+          <t>-2,77; 4,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 12,51</t>
+          <t>4,22; 12,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,01</t>
+          <t>1,9; 6,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,01</t>
+          <t>-1,47; 2,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 10,83</t>
+          <t>5,64; 10,81</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>650,12%</t>
+          <t>694,54%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>130,22%</t>
+          <t>130,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>206,52%</t>
+          <t>213,56%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,35; 1918,31</t>
+          <t>10,04; 1882,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>118,22; 2807,88</t>
+          <t>96,8; 3227,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,03; 190,97</t>
+          <t>4,13; 189,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,14; 121,68</t>
+          <t>-34,17; 96,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47,13; 274,37</t>
+          <t>44,88; 269,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,62; 246,11</t>
+          <t>35,92; 241,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,93; 105,2</t>
+          <t>-31,15; 101,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>104,73; 395,33</t>
+          <t>105,71; 371,47</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,82</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,71</t>
+          <t>5,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,82</t>
+          <t>-1,73; 3,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 3,14</t>
+          <t>-1,53; 3,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 9,92</t>
+          <t>1,86; 8,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,44; 13,13</t>
+          <t>5,18; 13,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 5,46</t>
+          <t>-1,07; 5,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 7,33</t>
+          <t>1,91; 8,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,19</t>
+          <t>2,52; 7,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,68</t>
+          <t>-0,51; 3,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,29</t>
+          <t>2,96; 7,56</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>273,72%</t>
+          <t>235,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>118,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>141,55%</t>
+          <t>157,01%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-65,08; 290,89</t>
+          <t>-60,54; 349,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,32; 349,65</t>
+          <t>-54,87; 310,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56,76; 893,48</t>
+          <t>31,67; 696,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77,55; 426,51</t>
+          <t>79,17; 450,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 171,81</t>
+          <t>-23,58; 172,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 222,67</t>
+          <t>23,13; 279,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,53; 280,99</t>
+          <t>53,83; 301,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 148,75</t>
+          <t>-13,31; 150,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>46,24; 300,06</t>
+          <t>67,06; 328,0</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-1,95</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,07</t>
+          <t>-2,86</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,56</t>
+          <t>-2,28</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 5,67</t>
+          <t>-2,02; 5,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 6,07</t>
+          <t>-2,11; 5,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 0,71</t>
+          <t>-4,97; 0,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,24; 16,75</t>
+          <t>2,85; 16,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 8,82</t>
+          <t>-3,53; 8,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 0,7</t>
+          <t>-8,29; 1,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 10,33</t>
+          <t>1,76; 9,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,9</t>
+          <t>-2,01; 5,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 0,17</t>
+          <t>-5,66; 0,36</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-51,98%</t>
+          <t>-56,16%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-39,56%</t>
+          <t>-27,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-36,99%</t>
+          <t>-33,01%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,84; 331,99</t>
+          <t>-44,59; 280,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,75; 361,33</t>
+          <t>-43,34; 335,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-87,52; 53,51</t>
+          <t>-90,24; 50,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23,17; 225,66</t>
+          <t>20,84; 244,89</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 127,5</t>
+          <t>-27,7; 115,62</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-72,45; 6,13</t>
+          <t>-58,87; 30,44</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,24; 204,62</t>
+          <t>18,37; 186,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 120,23</t>
+          <t>-22,07; 110,85</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-64,5; 5,33</t>
+          <t>-60,34; 7,76</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>9,42</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,49</t>
+          <t>9,3</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9,39</t>
+          <t>9,3</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,83</t>
+          <t>1,85; 7,95</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,16</t>
+          <t>0,03; 4,28</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,49; 12,91</t>
+          <t>6,4; 12,77</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,94; 12,37</t>
+          <t>2,48; 12,45</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,67; 11,73</t>
+          <t>2,06; 12,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,05; 13,51</t>
+          <t>5,03; 13,14</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,28</t>
+          <t>3,2; 8,81</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,42</t>
+          <t>1,89; 7,39</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6,56; 12,22</t>
+          <t>6,65; 11,76</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1344,22%</t>
+          <t>1337,04%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>169,39%</t>
+          <t>166,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>294,69%</t>
+          <t>291,83%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30,2; —</t>
+          <t>47,14; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-79,24; —</t>
+          <t>-60,91; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>216,38; —</t>
+          <t>281,45; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28,98; 327,98</t>
+          <t>26,59; 321,85</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30,21; 327,45</t>
+          <t>22,95; 316,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>63,28; 381,21</t>
+          <t>56,37; 345,79</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>59,16; 430,36</t>
+          <t>66,36; 389,49</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>36,19; 336,58</t>
+          <t>42,28; 319,03</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>142,63; 586,33</t>
+          <t>148,03; 564,74</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4,28</t>
+          <t>4,32</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,21</t>
+          <t>5,77</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,9</t>
+          <t>0,08; 4,54</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,31</t>
+          <t>-2,47; 0,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,74; 7,01</t>
+          <t>2,05; 7,04</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,04</t>
+          <t>-1,95; 4,06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 3,9</t>
+          <t>-2,68; 3,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 8,46</t>
+          <t>3,84; 10,34</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,47</t>
+          <t>-0,38; 3,42</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,04</t>
+          <t>-1,89; 1,79</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,36; 6,8</t>
+          <t>3,77; 7,58</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>143,79%</t>
+          <t>145,07%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>104,12%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 245,98</t>
+          <t>-1,83; 198,71</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-62,41; 67,56</t>
+          <t>-63,45; 47,59</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>42,03; 329,15</t>
+          <t>46,59; 330,14</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 62,28</t>
+          <t>-21,86; 62,26</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 60,31</t>
+          <t>-28,54; 49,99</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 115,9</t>
+          <t>37,83; 159,99</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 75,96</t>
+          <t>-5,87; 72,32</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 43,72</t>
+          <t>-30,3; 38,24</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>10,62; 139,85</t>
+          <t>57,21; 163,51</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>-0,73</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,29</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>1,85</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,0; -0,69</t>
+          <t>-5,02; -0,8</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 0,49</t>
+          <t>-3,81; 0,49</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 0,58</t>
+          <t>-2,96; 1,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,91</t>
+          <t>-1,78; 3,75</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,96; 7,09</t>
+          <t>1,04; 7,15</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,87</t>
+          <t>1,29; 7,15</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,02</t>
+          <t>-2,66; 0,9</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,36</t>
+          <t>-0,51; 3,34</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 2,61</t>
+          <t>0,15; 3,59</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-35,14%</t>
+          <t>-12,48%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-70,85; -13,4</t>
+          <t>-70,1; -15,5</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-55,78; 15,02</t>
+          <t>-53,01; 11,53</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-74,72; 10,4</t>
+          <t>-43,86; 37,41</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 60,95</t>
+          <t>-20,29; 60,79</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,86; 115,26</t>
+          <t>9,6; 121,56</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,22; 115,72</t>
+          <t>14,08; 120,56</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-33,45; 17,65</t>
+          <t>-33,99; 16,48</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 58,72</t>
+          <t>-6,7; 57,87</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 42,04</t>
+          <t>2,24; 63,77</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>2,99</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>3,85</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,98</t>
+          <t>0,1; 2,01</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,94</t>
+          <t>-0,74; 1,01</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,7</t>
+          <t>1,95; 4,04</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,24</t>
+          <t>2,49; 5,19</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,07</t>
+          <t>1,12; 3,99</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,9</t>
+          <t>3,37; 6,0</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,31</t>
+          <t>1,65; 3,36</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,28</t>
+          <t>0,54; 2,23</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,14</t>
+          <t>2,99; 4,66</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>1,93; 73,93</t>
+          <t>0,43; 74,85</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 34,96</t>
+          <t>-21,42; 38,12</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>38,28; 132,47</t>
+          <t>54,72; 152,84</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>28,59; 76,61</t>
+          <t>30,21; 74,69</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>13,83; 60,88</t>
+          <t>13,69; 57,96</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>16,31; 69,48</t>
+          <t>40,07; 86,59</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>27,85; 64,98</t>
+          <t>28,41; 67,65</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>11,55; 45,31</t>
+          <t>9,0; 45,16</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>33,54; 82,09</t>
+          <t>51,88; 95,39</t>
         </is>
       </c>
     </row>
